--- a/outputs/regression_output.xlsx
+++ b/outputs/regression_output.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>2026-03-08 23:15:53</t>
+          <t>2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>

--- a/outputs/regression_output.xlsx
+++ b/outputs/regression_output.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>2026-03-08 22:45:01</t>
+          <t>2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:11</t>
         </is>
       </c>
     </row>

--- a/outputs/regression_output.xlsx
+++ b/outputs/regression_output.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>2026-03-08 23:08:10</t>
+          <t>2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:11</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>

--- a/outputs/regression_output.xlsx
+++ b/outputs/regression_output.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:35</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>2026-03-08 23:10:45</t>
+          <t>2026-03-08 23:24:35</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:35</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:35</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:35</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:35</t>
         </is>
       </c>
     </row>

--- a/outputs/regression_output.xlsx
+++ b/outputs/regression_output.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:35</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>2026-03-08 23:24:35</t>
+          <t>2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:35</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:35</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:35</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:35</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
